--- a/data/env_test/case_excle/CompanyPurcharsWT/case_data_CompanyWT.xlsx
+++ b/data/env_test/case_excle/CompanyPurcharsWT/case_data_CompanyWT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/CompanyPurcharsWT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\InterfaceAutomaticTesttPlatform\data\env_test\case_excle\CompanyPurcharsWT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DBA9D0-0FE9-6845-93A1-C6A52540ABD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF72B4AD-AF27-47EB-8A24-CB3519E770F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43420" yWindow="4920" windowWidth="36000" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20325" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公开" sheetId="10" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="200">
   <si>
     <t>编号</t>
   </si>
@@ -154,75 +154,75 @@
   </si>
   <si>
     <t>{}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>查询标段信息</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"tfId":"$.data"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["操作成功!","==","$.msg","str"],[200,"==","$.code","int"]]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>提交采购公告</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>flowable/task/complete</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>发布公告</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{ "id": "${bulletinId}"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"token": "$.data.access_token"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbuser/login</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>招标人登录</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"username":"${username}","password":"${password}","identity": "1"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderFile</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>创建项目</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>查询项目</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"bidSectionId":"$.data.list[0].id","bidSectionCode":"$.data.list[0].bidSectionCode","bidSectionName":"$.data.list[0].bidSectionName"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"businessKey": "${tpId}"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>审批人登录</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>a3</t>
@@ -241,46 +241,46 @@
   </si>
   <si>
     <t>{"Aprtoken": "$.data.access_token"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"Authorization": "Bearer ${Aprtoken}","identityRole":"trade-audit"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"username":"${firstAprUser}","password":"${firstAprPsw}","identity": "1"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[{"ifBidPrice":"true","ifRequired":"true","fieldName":"单价","fieldType":"1","bidPriceType":"0","fieldUnit":"元","note":"请输入单价","tfId":"${tfId}"},{"ifBidPrice":"false","ifRequired":"true","fieldName":"质量","fieldType":"2","bidPriceType":"2","fieldUnit":"无","note":"请输入质量标准","tfId":"${tfId}"}]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tfEvaluateMethod/setup</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tfCatalog?tfId=${tfId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"methodName":"1","reviewer":"0","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","scorePrincipleType":"0","scaleProcess":"2","ifOfferRank":"false","ifWeight":"false","creditScoreParam":"{}","ifCreditScore":"false","creditWeight":"","ifCreditWeight":"false","ifSupportPreviewSumScore":"false","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":"1","ifOpenComputeChange":"false","isExpand":"false","stepName":"测试","sort":"1","stepType":"0","items":[{"itemName":"测试资格评审项","itemStandard":"测试资格评审项"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":"1","ifOpenComputeChange":"false","isExpand":"false","stepName":"价格","sort":"2","stepType":"2","standardScore":"100","catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":100,\"catalogId\":\"${catalogId}\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"computeFunType\":1,\"ruleContent\":\"以有效最低价为基准价，得最高分Fmax，计算公式：价格得分=（评标基准价/评标报价）*最高分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"urlResized":"","image":{},"isPlayingAv":"false","oldFileName":"","oldCustomName":"","upload":{"data":"","error":"false"},"lastKnownSrc":"","raw":{"status":"parsing"},"server":{"status":"parsing"},"file":{"status":"parsing"},"thumbnailSize":360,"read":"false","dimensions":{"width":0,"height":0},"error":"false","options":{"read":"","maxSize":"","accept":"","thumbnailSize":"","averageColor":"","withCredentials":""},"maxSize":"","accept":"","id":"0.805626534524633:1736925993363","calculateAverageColor":"","fileSize":348843,"status":"uploading","fileMd5":"43390c888cdd9d2d688ba83826ed6448","fileSuffix":"application/pdf","chunkCount":1,"progress":0,"downloadProgress":0,"fileName":"投标文件正文.pdf","replaceVisitEndpoint":"http://minio.zszc.jianshicha.cn"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"fileId":"$.data.id"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["秒传","==","$.msg","str"],[200,"==","$.code","int"],["$.data.id","==","${fileId}","str"]]</t>
   </si>
   <si>
     <t>brace/file/upload/resume/chunk</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>brace/file/extension/uploadToPdfById?fileId=${fileId}</t>
@@ -314,47 +314,47 @@
   </si>
   <si>
     <t>[{"fileId":"${fileId}","fileType":1,"tfId":"${tfId}"}]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderFile/step?tfId=${tfId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderFile/pack?id=${tfId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderFile/submit?ifSubmit=true&amp;id=${tfId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["转换pdf并上传成功","==","$.msg","str"],[200,"==","$.code","int"],["$.data.id","==","${fileId}","str"]]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["操作成功!","==","$.msg","str"],[200,"==","$.code","int"],["$.data.tfId","==","${tfId}","str"]]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>文件预上传</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderFile/check?id=${tfId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>审批-招标文件</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"businessKey": "${tfId}"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>审批-项目创建</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>a8</t>
@@ -364,43 +364,43 @@
   </si>
   <si>
     <t>{"tpId":"$.data.list[0].id","purchaseProjectCode":"$.data.list[0].purchaseProjectCode"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderBulletin?submit=true</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>审批-招标公告</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"businessKey": "${bulletinId}"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderBulletin/submit</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>设置开标一览表-catalogId</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>查询招标公告</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderBulletin/page?current=1&amp;size=10&amp;total=1&amp;state=1&amp;sectionType=2&amp;bulletinType=4&amp;tenderProId=${tpId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"bulletinId":"$.data.[0].bulletinId"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>设置开标一览表</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>a22</t>
@@ -410,67 +410,67 @@
   </si>
   <si>
     <t>etbtrade/tfCatalog/bid/${tfId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"catalogId":"$.data.[0].id"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"marginPrice":"${marginPrice}","marginUnit":"${marginUnit}","bidLimitpriceUnit":"1","ifJudgesConfirmWinBidder":"${ifJudgesConfirmWinBidder}","ifShortlistedProject":"false","ifSyndicatedFlag":"${ifSyndicatedFlag}","ifSupportSmallMicro":"${ifSupportSmallMicro}","ifSupportBlindBid":"${ifSupportBlindBid}","ifDoubleEnvelope":"false","guaranteeTypeArr":[${ifFee}],"promiseLetterTemplateName":"","ifVerifyBasicAccount":"false","ifOpenCreditScoreReject":"false","ifSameSerialNum":"false","tfPrice":"${tfPrice}","ifCiphertextLetter":"false","vaildPeriod":"90","openMinLimit":"3","evalMinLimit":"3","fileJmDuration":"30","bidSectionId":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","tpName":"${purchaseProjectName}","tfName":"${bidSectionName}","address":"测试","bidOpeningType":"1","evaluationType":"1","bidLimitpriceHighest":"344","bidEvaluateRoom":"","bidOpeningRoom":"","payDesc":"测试","fileQuestionEndTime":"${docGetEndTime}","guaranteeType":"${guaranteeType}","tpId":"${tpId}","bidOpeningPoint":"测试","ifUseCa":"${ifUseCa}"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"invitationType":"normal","ifSyndicatedFlag1":"0","projectName":"${purchaseProjectName}","projectCode":"${purchaseProjectCode}","bidSectionName":"${bidSectionName}","bidSectionCode":"${bidSectionCode}","fileTimes":["${noticeSendTime}","${noticeEndTime}"],"tenderContactName":"测试","tenderContactPhone":"13000000001","content":"测试","fileIds":"","projectId":"${tpId}","bidSectionId":"${bidSectionId}","projectType":"2","qualityQueryType":2,"publishStatus":1,"ifDrawingDeposit":0,"ifFileFee":0,"tenderFileBeginTime":"${noticeSendTime}","tenderFileEndTime":"${noticeEndTime}","businessList":[{"id":"1824262397682434049","businessName":"tbr1","businessType":175,"unifiedSocialCreditCode":"92310000UHU0FJ324B","industryType":"A,A01","foundAddress":"","officeAddress":"中国,13,1301,130102","quHuaAddress":"中国河北省石家庄市长安区","detailedAddress":"","businessScope":"经营范围：大三的课i及防水等级等方式尽快顺丰快递、的、广泛的、是、的功夫、供奉的是、高峰时段、告诉对方、多个省份、三个地方、受到广泛、高峰时段、对方是个、告诉对方、告诉对方、、脚后跟、和可见光、再、一天天、、部分读书报告、、垦局、看","amount":"5000.0000","currencyUnit":1,"currency":"156","foundTime":"","insertTime":"2024-10-18 16:50:34","ifBusiness":"","businessStartTime":"","businessEndTime":"","legalPersonName":"卜清妍","legalPersonIdType":"","legalPersonIdCode":"","legalPersonPhone":"13288105370","businessContactName":"卜清妍","businessContactPhone":"13288105370","businessContactIdType":8,"businessContactIdCode":"420101198101010918","businessContactAddress":"河北省石家庄市裕华区","businessEmail":"125254@12.com","businessBank":"中国人民银行","businessBankCode":"5363095176301","basicBankCode":"5363095176301","fileIds":"7bc4a44350cbbc23d87351dbba25f45f","submitTime":"2024-10-18 16:50:34","auditStatus":2,"auditOpinion":"","submit":"","businessShortName":"","businessFax":"","businessLogo":"","businessContactSex":"","legalPersonSex":"","legalPersonEmail":"","registrationType":0,"enterType":1,"zipCode":"054100","businessUrl":"","identityRole":"","disabledState":0,"identities":[{"biId":"1824262397682434049","identityName":"投标人","ecode":"","identityCode":"IdentityRole_8","grade":"0"}],"scfEnterpriseName":"","ifHoldCA":"","businessNo":"20240816000003","companyStatus":"","publicBankCode":"","bankBranchProvincesCode":"","bankBranchProvincesName":"","bankBranchName":"","publicBankNo":"","accountOpeningPermit":"","remitBusinessId":"","remitAmount":"","extendedFields":"","fileJson":"","businessApprovalStatus":"","businessApprovalFinishTime":"2024-08-16 09:58:31","ifAudit":"","enterpriseEcode":"","certificateQualificationJson":"","performanceInformationJson":"","companyProfile":"","organizationCode":"","creditRate":"02","caCode":"","taxRegisterCode":"","businessLicenseCode":""},{"id":"1824265751921868802","businessName":"tbr3","businessType":175,"unifiedSocialCreditCode":"933301009YHAG7RT51","industryType":"A,A04","foundAddress":"","officeAddress":"中国,13,1304,130403","quHuaAddress":"中国河北省邯郸市丛台区","detailedAddress":"","businessScope":"gfddgfsgdfs f 的风格、 、 、规范、供奉的是、广东佛山、 受到广泛、的高富帅、的高富帅、发生的刚送到规范、 的高富帅、 发电公司、的高富帅、","amount":"5000.0000","currencyUnit":1,"currency":"156","foundTime":"","insertTime":"2024-08-16 10:03:43","ifBusiness":"","businessStartTime":"","businessEndTime":"","legalPersonName":"罗晨璐","legalPersonIdType":"","legalPersonIdCode":"","legalPersonPhone":"13512425807","businessContactName":"罗晨璐","businessContactPhone":"13512425807","businessContactIdType":8,"businessContactIdCode":"35422543","businessContactAddress":"河北省邯郸市丛台区","businessEmail":"54325234@qq.com","businessBank":"中国人民银行","businessBankCode":"6222627649804139651","basicBankCode":"6222627649804139651","fileIds":"a83efbf23a28e4c0f973797e40c89d2f","submitTime":"2024-08-16 10:06:23","auditStatus":2,"auditOpinion":"1","submit":"","businessShortName":"","businessFax":"","businessLogo":"","businessContactSex":"","legalPersonSex":"","legalPersonEmail":"","registrationType":0,"enterType":1,"zipCode":"054000","businessUrl":"","identityRole":"","disabledState":0,"identities":[{"biId":"1824265751921868802","identityName":"投标人","ecode":"","identityCode":"IdentityRole_8","grade":"0"}],"scfEnterpriseName":"","ifHoldCA":"","businessNo":"20240816000005","companyStatus":"","publicBankCode":"","bankBranchProvincesCode":"","bankBranchProvincesName":"","bankBranchName":"","publicBankNo":"","accountOpeningPermit":"","remitBusinessId":"","remitAmount":"","extendedFields":"","fileJson":"","businessApprovalStatus":"","businessApprovalFinishTime":"2024-08-16 10:06:56","ifAudit":"","enterpriseEcode":"","certificateQualificationJson":"","performanceInformationJson":"","companyProfile":"","organizationCode":"","creditRate":"02","caCode":"","taxRegisterCode":"","businessLicenseCode":""},{"id":"1824265147837235202","businessName":"tbr2","businessType":175,"unifiedSocialCreditCode":"921200002BRBJCN07Q","industryType":"B,B06","foundAddress":"","officeAddress":"中国,13,1305,130582","quHuaAddress":"中国河北省邢台市沙河市","detailedAddress":"","businessScope":"范围：gdfdfsagdsfgsdfgdgfssdgfdgfsgdsfgdfsgfdsdgfsdgfsgfdsgfds的风格广东佛山给发生的故事的发的高富帅高峰时段刚送到发高峰时段规范、 广泛的、 广泛的、 规范、 给、 规范、 的高富帅、 、 给、 高峰时段、 受到广泛、 稍等、","amount":"5000.0000","currencyUnit":1,"currency":"156","foundTime":"","insertTime":"2024-08-16 10:01:19","ifBusiness":"","businessStartTime":"","businessEndTime":"","legalPersonName":"尹萌萌","legalPersonIdType":"","legalPersonIdCode":"","legalPersonPhone":"13514269122","businessContactName":"尹萌萌","businessContactPhone":"13514269122","businessContactIdType":8,"businessContactIdCode":"3254543435546","businessContactAddress":"河北省邢台市沙河市","businessEmail":"346675657@qq.com","businessBank":"中国人民银行","businessBankCode":"6225566301874193304","basicBankCode":"6225566301874193304","fileIds":"0155aaf8e6a7a2540b4e0fc2574f0e4b","submitTime":"2024-08-16 10:03:01","auditStatus":2,"auditOpinion":"","submit":"","businessShortName":"","businessFax":"","businessLogo":"","businessContactSex":"","legalPersonSex":"","legalPersonEmail":"","registrationType":0,"enterType":1,"zipCode":"054100","businessUrl":"","identityRole":"","disabledState":0,"identities":[{"biId":"1824265147837235202","identityName":"投标人","ecode":"","identityCode":"IdentityRole_8","grade":"0"}],"scfEnterpriseName":"","ifHoldCA":"","businessNo":"20240816000004","companyStatus":"","publicBankCode":"","bankBranchProvincesCode":"","bankBranchProvincesName":"","bankBranchName":"","publicBankNo":"","accountOpeningPermit":"","remitBusinessId":"","remitAmount":"","extendedFields":"","fileJson":"","businessApprovalStatus":"","businessApprovalFinishTime":"2024-08-16 10:06:56","ifAudit":"","enterpriseEcode":"","certificateQualificationJson":"","performanceInformationJson":"","companyProfile":"","organizationCode":"","creditRate":"02","caCode":"","taxRegisterCode":"","businessLicenseCode":""}],"tenderMode":2,"ifSyndicatedFlag":"${ifSyndicatedFlag}"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>brace/invitation</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>brace/invitation/page/tender?projectId=${tpId}&amp;current=1&amp;size=10&amp;total=1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>提交投标邀请函</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>查询投标邀请函</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>发布投标邀请函</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>brace/invitation/audit</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"inviteLetter":"$.data.[0].id"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"id":"${inviteLetter}","publishStatus":2}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>提交邀请公告</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderBulletin?submit=true</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderBulletin/page?current=1&amp;size=10&amp;total=1&amp;state=1&amp;sectionType=2&amp;bulletinType=5&amp;tenderProId=${tpId}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>b1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>b2</t>
@@ -548,89 +548,81 @@
     <t>b26</t>
   </si>
   <si>
-    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"1887306232988766210\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>etbtrade/tpPurchaseGov?submit=true</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tpPurchaseGov/page?current=1&amp;size=10&amp;total=40&amp;purchaseProjectName=${purchaseProjectNameDecode}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/section/page?tpId=${tpId}&amp;tpType=1&amp;current=1&amp;size=10&amp;total=0</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"tenderProName":"${purchaseProjectName}","tenderProCode":"${purchaseProjectCode}","gpBudget":"2344万元","limitedPrice":"344万元","getDocAddr":"沙河市阳光招采平台（http://www.jy.jiezhaowang.com）","submitAddr":"测试","projectContact":"测试","projectContactTel":"13000000001","tfPrice":"200元","ifSyndicatedFlag":0,"ifSyndicatedFlagCus":"拒绝","noticeName":"测试","purchaseContent":"测试","supplierQualification":"测试","contractTerm":"测试","spSupplierQualification":"测试","docGetStartTime":"${noticeSendTime}","docGetStartTimeCus":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","docGetEndTimeCus":"${noticeEndTime}","startMor":"00:11:08","startMorCus":"00:11:08","endMor":"12:00:00","endMorCus":"12:00:00","startAfter":"12:11:20","startAfterCus":"12:11:20","endAfter":"23:11:26","endAfterCus":"23:11:26","tenderDocGetMethodStr":"测试","bidOpenTime":"${noticeEndTime}","bidOpenTimeCus":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","bidDocReferEndTimeCus":"${noticeEndTime}","bidOpenAddr":"测试","remark":"测试","collectName":"测试","collectPersonAddr":"测试","collectPersonTel":"13000000001","openType":0,"bulletinMediaCus":["1722594868247506946"],"noticeNature":0,"tenderProType":"1","tenderProId":"${tpId}","bidMode":"${purchaseMode}","bulletinType":4,"sectionType":2,"regionName":"河北省-唐山市-路北区","regionCode":"130203","challengeCall":"13000000001","tenderDocGetMethod":1,"sectionIds":"${bidSectionId}","bulletinMedia":"1722594868247506946","hostId":"1825731873402441728","hostName":"${username}","hostTelephone":"13085840000","hostOrgId":"10000-000132","noticeTime":["${noticeSendTime}","${noticeEndTime}"],"bidDocReferMethod":"1","sectionList":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"sectionListCus":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"noticeSendTime":"${noticeSendTime}","noticeEndTime":"${noticeEndTime}","noticeContent":"&lt;div data-v-148f4874=\"\" id=\"editorContent\" style=\"overflow-wrap: break-word; word-break: break-all; font-family: 微软雅黑;\"&gt;&lt;h3 data-v-148f4874=\"\" style=\"text-align: center;\"&gt;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/h3&gt; &lt;h4 data-v-148f4874=\"\"&gt;项目概况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt; 招标项目的潜在投标人应在&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; 获取招标文件，并于&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;前递交投标文件。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;一、项目基本情况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;项目编号： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${tpId}&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;项目名称：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;预算金额： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;2344万元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;最高限价： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;344万元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: SimHei, sans-serif;\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;, &amp;quot;Helvetica Neue&amp;quot;, &amp;quot;PingFang SC&amp;quot;, sans-serif;\"&gt;采购需求： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;, &amp;quot;Helvetica Neue&amp;quot;, &amp;quot;PingFang SC&amp;quot;, sans-serif;\"&gt;合同履行期限：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;本项目&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;拒绝&lt;/span&gt; 联合体投标&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;二、申请人的资格要求&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;1、法律规定：满足《中华人民共和国政府采购法》第二十二条规定;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;2、落实政府采购政策需满足的资格要求：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;3、本项目的特定要求：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;三、获取招标文件&lt;/h4&gt; &lt;p data-v-148f4874=\"\" style=\"line-height: 2;\"&gt;时间：&lt;span data-v-148f4874=\"\"&gt;${noticeSendTime}&lt;/span&gt;&amp;nbsp; 至 &lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;，每天上午 &lt;span data-v-148f4874=\"\"&gt;00:11:08&lt;/span&gt;&amp;nbsp;- &lt;span data-v-148f4874=\"\"&gt;12:00:00&lt;/span&gt;&amp;nbsp;，下午 &lt;span data-v-148f4874=\"\"&gt;12:11:20&lt;/span&gt;&amp;nbsp;- &lt;span data-v-148f4874=\"\"&gt;23:11:26&lt;/span&gt;&amp;nbsp;（北京时间，法定节假日除外）&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;沙河市阳光招采平台（http://www.jy.jiezhaowang.com）&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;方式:&amp;nbsp; &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;售价：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;200元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;四、响应文件提交&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;截止时间：&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;五、开启&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;时间：&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;公告期限&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;自本公告发布之日起5个工作日。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;六、其他补充事项&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;七、对本次招标提出询问，请按以下方式联系&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;1.采购人信息&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 名&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;称： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 地&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;址：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; &amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 联系方式：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;2.项目联系方式&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 项目负责人： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 联 系 方 式：&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;/h4&gt;&lt;/div&gt;","templateDetailId":"1879804151350157313"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"sectionIds":"${bidSectionId}","noticeSendTime":"${noticeSendTime}","noticeEndTime":"${noticeEndTime}","docGetStartTime":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","tenderProId":"${tpId}","noticeContent":"&lt;p&gt;测试公告内容！！！&lt;/p&gt;","openType":"0","bulletinMedia1":["1722594868247506946"],"tenderProName":"${purchaseProjectName}","noticeNature":"0","bulletinType":"5","bidMode":"1","tenderProCode":"${purchaseProjectCode}","tenderProType":"1","regionCode":"130203","regionName":"河北省-唐山市-路北区","tradeCenterName":"","bulletinMedia":"1722594868247506946","noticeName":"测试","docTime":["${noticeSendTime}","${noticeEndTime}"],"noticeTime":["${noticeSendTime}","${noticeEndTime}"],"tenderDocGetMethod":"1","bidDocReferMethod":"1","bidDocReferEndTime":"${noticeEndTime}","bidOpenTime":"${noticeEndTime}","challengeCall":"13000000001","hostId":"1825731873402441728","hostName":"招标人AAA","hostTelephone":"13085840000","hostOrgId":"10000-000132","attachmentIds":"","sectionType":2}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>{"paName":"","paCode":"","pqrMode":"${pqrMode}","ifIn":"false","ifRequiredTender":"true","ifPpp":"false","ifEEvaluation":"true","ifReserveField":"false","ifPushProvincePsp":"true","ifPushChinaPublicService":"true","tenderOrganizeForm":"${tenderOrganizeForm}","purchaseOrganizeForm":"2","inviteType":"${inviteType}","budgetDepartmentUnitType":"1","typeAttachment":[],"priceFrom":"1","priceDiscountRate":"","purchaseProjectName":"政采-${purchaseProjectName}","regionCodeShowCus":["13","1302","130203"],"regionCodeShow":"13-1301-130102","regionCode":"130102","regionName":"河北省-石家庄市-长安区","purchasePlanCode":"457484584501","unitBudget":"1","budget":"2344","affiliatedCompanyCus":"测试自动化专用企业","industriesTypeCus":["D","D44"],"industriesType":"D-D44","industriesTypeName":"电力、热力、燃气及水生产和供应业-电力、热力生产和供应业","purchaseProjectType":"${purchaseProjectType}","purchaseMode":"${purchaseMode}","purchaseContent":"测试","purchaserLxr":"测试","purchaserLxrTelephone":"13000000001","superviseUnitName":"监管人","superviseUnitCode":"931100000Y8C6DR0XT","transactionCenter":"无极金融服务平台交易中心","transactionCenterCode":"13012","transactionCenterCus":["13012"],"sectionList":[{"bidSectionDesc":"政采-${purchaseProjectName}-标段01","bidderCondition":"政采-${purchaseProjectName}-标段01","ifSignUpApprove":"false","bidSectionName":"政采-${purchaseProjectName}-标段01","classifyCodeCus":["B","B02","B0201","B020102"],"classifyCode":"B-B02-B0201-B020102","investBudget":"344","customId":"46241736127869061","bidSectionCode":"-","classifyName":"货物类-医疗器械-医疗器械-注射穿刺器械"},{"bidSectionDesc":"政采-${purchaseProjectName}-标段02","bidderCondition":"政采-${purchaseProjectName}-标段02","ifSignUpApprove":"false","bidSectionName":"政采-${purchaseProjectName}-标段02","classifyCodeCus":["B","B03","B0303","B030302"],"classifyCode":"B-B03-B0303-B030302","investBudget":"544","customId":"79531736127886926","bidSectionCode":"-","classifyName":"货物类-金属材料-合金-有色金属合金"}],"investCodeType":"2","affiliatedCompany":"测试自动化专用企业"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>代理信息查询</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbuser/user/single</t>
   </si>
   <si>
     <t>招标人信息查询</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>brace/business/query/page?roleType=IdentityRole_1&amp;current=1&amp;size=10&amp;total=0</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>预上传代理合同</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>brace/file/upload/resume/chunk</t>
   </si>
   <si>
     <t>{"purchaserName":"$.data.list[0].businessName","purchaserCode":"$.data.list[0].unifiedSocialCreditCode","purchaserLxr":"$.data.list[0].businessContactName","purchaserLxrTelephone":"$.data.list[0].businessContactPhone"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"urlResized":"","image":{},"isPlayingAv":"false","oldFileName":"","oldCustomName":"","upload":{"data":"","error":"false"},"lastKnownSrc":"","raw":{"status":"parsing"},"server":{"status":"parsing"},"file":{"status":"parsing"},"thumbnailSize":360,"read":"false","dimensions":{"width":0,"height":0},"error":"false","options":{"read":"","maxSize":"","accept":"","thumbnailSize":"","averageColor":"","withCredentials":""},"maxSize":"","accept":"","id":"0.8860670692696713:1739606692885","calculateAverageColor":"","fileSize":355755,"status":"uploading","fileMd5":"7d28ec917528c327e4afce91d7c0a222","fileSuffix":"application/pdf","chunkCount":1,"progress":0,"downloadProgress":0,"fileName":"测试中通采购项目.pdf","replaceVisitEndpoint":"http://minio.zszc.jianshicha.cn"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"attachmentId":"$.data.id"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["操作成功","==","$.msg","str"],[200,"==","$.code","int"]]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["查询成功","==","$.msg","str"],[200,"==","$.code","int"]]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[["秒传","==","$.msg","str"],[200,"==","$.code","int"]]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"Authorization": "Bearer ${token}","identityRole":"IdentityRole_2"}</t>
   </si>
   <si>
     <t>{"Authorization": "Bearer ${token}","identityRole":"IdentityRole_2"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{"paName":"$.data.name","paCode":"$.data.ecode"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>a20</t>
@@ -691,39 +683,54 @@
   </si>
   <si>
     <t>{"paName":"${paName}","paCode":"${paCode}","pqrMode":"${pqrMode}","ifIn":"false","ifRequiredTender":"true","ifPpp":"false","ifEEvaluation":"true","ifReserveField":"false","ifPushProvincePsp":"true","ifPushChinaPublicService":"true","tenderOrganizeForm":"${tenderOrganizeForm}","purchaseOrganizeForm":"2","inviteType":"${inviteType}","budgetDepartmentUnitType":"1","typeAttachment":[{"name":"委托合同","type":"3","attachment":"${attachmentId}"}],"priceFrom":"1","priceDiscountRate":"","purchaseProjectName":"企采-${purchaseProjectName}","regionCodeShowCus":["13","1302","130203"],"regionCodeShow":"13-1301-130102","regionCode":"130102","regionName":"河北省-石家庄市-长安区","purchasePlanCode":"457484584501","unitBudget":"1","budget":"2344","affiliatedCompanyCus":"测试自动化专用企业","industriesTypeCus":["D","D44"],"industriesType":"D-D44","industriesTypeName":"电力、热力、燃气及水生产和供应业-电力、热力生产和供应业","purchaseProjectType":"${purchaseProjectType}","purchaseMode":"${purchaseMode}","purchaseContent":"测试","paLxr":"测试","paLxrTelephone":"13000000001","purchaserName":"${purchaserName}","purchaserCode":"${purchaserCode}","purchaserLxr":"${purchaserLxr}","purchaserLxrTelephone":"${purchaserLxrTelephone}","superviseUnitName":"监管人","superviseUnitCode":"931100000Y8C6DR0XT","transactionCenter":"无极金融服务平台交易中心","transactionCenterCode":"13012","transactionCenterCus":["13012"],"sectionList":[{"bidSectionDesc":"企采-${purchaseProjectName}-标段01","bidderCondition":"企采-${purchaseProjectName}-标段01","ifSignUpApprove":"false","bidSectionName":"企采-${purchaseProjectName}-标段01","classifyCodeCus":["B","B02","B0201","B020102"],"classifyCode":"B-B02-B0201-B020102","investBudget":"344","customId":"46241736127869061","bidSectionCode":"-","classifyName":"货物类-医疗器械-医疗器械-注射穿刺器械"},{"bidSectionDesc":"企采-${purchaseProjectName}-标段02","bidderCondition":"企采-${purchaseProjectName}-标段02","ifSignUpApprove":"false","bidSectionName":"企采-${purchaseProjectName}-标段02","classifyCodeCus":["B","B03","B0303","B030302"],"classifyCode":"B-B03-B0303-B030302","investBudget":"544","customId":"79531736127886926","bidSectionCode":"-","classifyName":"货物类-金属材料-合金-有色金属合金"}],"investCodeType":"2","affiliatedCompany":"测试自动化专用企业"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>获取当前用户信息</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>etbtrade/tenderBulletin/getUserList</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"hostId":"$.data[0].userId","hostName":"$.data[0].name","hostOrgId":"$.data[0].orgCode"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"tenderProName":"${purchaseProjectName}","tenderProCode":"${purchaseProjectCode}","gpBudget":"2344万元","limitedPrice":"344万元","getDocAddr":"沙河市阳光招采平台（http://www.jy.jiezhaowang.com）","submitAddr":"测试","projectContact":"测试","projectContactTel":"13000000001","tfPrice":"200元","ifSyndicatedFlag":0,"ifSyndicatedFlagCus":"拒绝","noticeName":"测试","purchaseContent":"测试","supplierQualification":"测试","contractTerm":"测试","spSupplierQualification":"测试","docGetStartTime":"${noticeSendTime}","docGetStartTimeCus":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","docGetEndTimeCus":"${noticeEndTime}","startMor":"00:11:08","startMorCus":"00:11:08","endMor":"12:00:00","endMorCus":"12:00:00","startAfter":"12:11:20","startAfterCus":"12:11:20","endAfter":"23:11:26","endAfterCus":"23:11:26","tenderDocGetMethodStr":"测试","bidOpenTime":"${noticeEndTime}","bidOpenTimeCus":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","bidDocReferEndTimeCus":"${noticeEndTime}","bidOpenAddr":"测试","remark":"测试","collectName":"测试","collectPersonAddr":"测试","collectPersonTel":"13000000001","agencyFullName": "测试","agencyAddr": "测试","agencyContactTel": "13000000001","openType":0,"bulletinMediaCus":["1722594868247506946"],"noticeNature":0,"tenderProType":"2","tenderProId":"${tpId}","bidMode":"${purchaseMode}","bulletinType":4,"sectionType":2,"regionName":"河北省-唐山市-路北区","regionCode":"130203","challengeCall":"13000000001","tenderDocGetMethod":1,"sectionIds":"${bidSectionId}","bulletinMedia":"1722594868247506946","hostId":"${hostId}","hostName":"${hostName}","hostTelephone":"13085840000","hostOrgId":"${hostOrgId}","noticeTime":["${noticeSendTime}","${noticeEndTime}"],"bidDocReferMethod":"1","sectionList":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"sectionListCus":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"noticeSendTime":"${noticeSendTime}","noticeEndTime":"${noticeEndTime}","noticeContent":"&lt;div data-v-148f4874=\"\" id=\"editorContent\" style=\"overflow-wrap: break-word; word-break: break-all; font-family: 微软雅黑;\"&gt;&lt;h3 data-v-148f4874=\"\" style=\"text-align: center;\"&gt;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/h3&gt; &lt;h4 data-v-148f4874=\"\"&gt;项目概况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt; 招标项目的潜在投标人应在&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; 获取招标文件，并于&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;前递交投标文件。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;&lt;h4 data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;/h4&gt;&lt;/div&gt;","templateDetailId":"1891395172940898305"}</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>a27</t>
+  </si>
+  <si>
+    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"${catalogId}\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"hostId":"$.data[0].userId","hostName":"$.data[0].name","hostOrgId":"$.data[0].orgCode","hostPhone":"$.data[0].phone"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"tenderProName":"${purchaseProjectName}","tenderProCode":"${purchaseProjectCode}","gpBudget":"2344万元","limitedPrice":"344万元","getDocAddr":"沙河市阳光招采平台（http://www.jy.jiezhaowang.com）","submitAddr":"测试","projectContact":"测试","projectContactTel":"13000000001","tfPrice":"200元","ifSyndicatedFlag":0,"ifSyndicatedFlagCus":"拒绝","noticeName":"测试","purchaseContent":"测试","supplierQualification":"测试","contractTerm":"测试","spSupplierQualification":"测试","docGetStartTime":"${noticeSendTime}","docGetStartTimeCus":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","docGetEndTimeCus":"${noticeEndTime}","startMor":"00:11:08","startMorCus":"00:11:08","endMor":"12:00:00","endMorCus":"12:00:00","startAfter":"12:11:20","startAfterCus":"12:11:20","endAfter":"23:11:26","endAfterCus":"23:11:26","tenderDocGetMethodStr":"测试","bidOpenTime":"${noticeEndTime}","bidOpenTimeCus":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","bidDocReferEndTimeCus":"${noticeEndTime}","bidOpenAddr":"测试","remark":"测试","collectName":"测试","collectPersonAddr":"测试","collectPersonTel":"13000000001","agencyFullName": "测试","agencyAddr": "测试","agencyContactTel": "13000000001","openType":0,"bulletinMediaCus":["1722594868247506946"],"noticeNature":0,"tenderProType":"2","tenderProId":"${tpId}","bidMode":"${purchaseMode}","bulletinType":4,"sectionType":2,"regionName":"河北省-唐山市-路北区","regionCode":"130203","challengeCall":"13000000001","tenderDocGetMethod":1,"sectionIds":"${bidSectionId}","bulletinMedia":"1722594868247506946","hostId":"${hostId}","hostName":"${hostName}","hostTelephone":"${hostPhone}","hostOrgId":"${hostOrgId}","noticeTime":["${noticeSendTime}","${noticeEndTime}"],"bidDocReferMethod":"1","sectionList":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"sectionListCus":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"noticeSendTime":"${noticeSendTime}","noticeEndTime":"${noticeEndTime}","noticeContent":"&lt;div data-v-148f4874=\"\" id=\"editorContent\" style=\"overflow-wrap: break-word; word-break: break-all; font-family: 微软雅黑;\"&gt;&lt;h3 data-v-148f4874=\"\" style=\"text-align: center;\"&gt;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/h3&gt; &lt;h4 data-v-148f4874=\"\"&gt;项目概况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt; 招标项目的潜在投标人应在&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; 获取招标文件，并于&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;前递交投标文件。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;&lt;h4 data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;/h4&gt;&lt;/div&gt;","templateDetailId":"1891395172940898305"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"tenderProName":"${purchaseProjectName}","tenderProCode":"${purchaseProjectCode}","gpBudget":"2344万元","limitedPrice":"344万元","getDocAddr":"沙河市阳光招采平台（http://www.jy.jiezhaowang.com）","submitAddr":"测试","projectContact":"测试","projectContactTel":"13000000001","tfPrice":"200元","ifSyndicatedFlag":0,"ifSyndicatedFlagCus":"拒绝","noticeName":"测试","purchaseContent":"测试","supplierQualification":"测试","contractTerm":"测试","spSupplierQualification":"测试","docGetStartTime":"${noticeSendTime}","docGetStartTimeCus":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","docGetEndTimeCus":"${noticeEndTime}","startMor":"00:11:08","startMorCus":"00:11:08","endMor":"12:00:00","endMorCus":"12:00:00","startAfter":"12:11:20","startAfterCus":"12:11:20","endAfter":"23:11:26","endAfterCus":"23:11:26","tenderDocGetMethodStr":"测试","bidOpenTime":"${noticeEndTime}","bidOpenTimeCus":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","bidDocReferEndTimeCus":"${noticeEndTime}","bidOpenAddr":"测试","remark":"测试","collectName":"测试","collectPersonAddr":"测试","collectPersonTel":"13000000001","openType":0,"bulletinMediaCus":["1722594868247506946"],"noticeNature":0,"tenderProType":"1","tenderProId":"${tpId}","bidMode":"${purchaseMode}","bulletinType":4,"sectionType":2,"regionName":"河北省-唐山市-路北区","regionCode":"130203","challengeCall":"13000000001","tenderDocGetMethod":1,"sectionIds":"${bidSectionId}","bulletinMedia":"1722594868247506946","hostId":"${hostId}","hostName":"${hostName}","hostTelephone":"${hostPhone}","hostOrgId":"${hostOrgId}","noticeTime":["${noticeSendTime}","${noticeEndTime}"],"bidDocReferMethod":"1","sectionList":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"sectionListCus":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"noticeSendTime":"${noticeSendTime}","noticeEndTime":"${noticeEndTime}","noticeContent":"&lt;div data-v-148f4874=\"\" id=\"editorContent\" style=\"overflow-wrap: break-word; word-break: break-all; font-family: 微软雅黑;\"&gt;&lt;h3 data-v-148f4874=\"\" style=\"text-align: center;\"&gt;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/h3&gt; &lt;h4 data-v-148f4874=\"\"&gt;项目概况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt; 招标项目的潜在投标人应在&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; 获取招标文件，并于&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;前递交投标文件。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;一、项目基本情况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;项目编号： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${tpId}&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;项目名称：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;预算金额： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;2344万元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;最高限价： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;344万元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: SimHei, sans-serif;\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;, &amp;quot;Helvetica Neue&amp;quot;, &amp;quot;PingFang SC&amp;quot;, sans-serif;\"&gt;采购需求： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;, &amp;quot;Helvetica Neue&amp;quot;, &amp;quot;PingFang SC&amp;quot;, sans-serif;\"&gt;合同履行期限：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;本项目&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;拒绝&lt;/span&gt; 联合体投标&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;二、申请人的资格要求&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;1、法律规定：满足《中华人民共和国政府采购法》第二十二条规定;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;2、落实政府采购政策需满足的资格要求：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;3、本项目的特定要求：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;三、获取招标文件&lt;/h4&gt; &lt;p data-v-148f4874=\"\" style=\"line-height: 2;\"&gt;时间：&lt;span data-v-148f4874=\"\"&gt;${noticeSendTime}&lt;/span&gt;&amp;nbsp; 至 &lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;，每天上午 &lt;span data-v-148f4874=\"\"&gt;00:11:08&lt;/span&gt;&amp;nbsp;- &lt;span data-v-148f4874=\"\"&gt;12:00:00&lt;/span&gt;&amp;nbsp;，下午 &lt;span data-v-148f4874=\"\"&gt;12:11:20&lt;/span&gt;&amp;nbsp;- &lt;span data-v-148f4874=\"\"&gt;23:11:26&lt;/span&gt;&amp;nbsp;（北京时间，法定节假日除外）&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;沙河市阳光招采平台（http://www.jy.jiezhaowang.com）&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;方式:&amp;nbsp; &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;售价：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;200元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;四、响应文件提交&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;截止时间：&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;五、开启&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;时间：&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;公告期限&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;自本公告发布之日起5个工作日。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;六、其他补充事项&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;七、对本次招标提出询问，请按以下方式联系&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;1.采购人信息&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 名&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;称： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 地&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;址：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; &amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 联系方式：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;2.项目联系方式&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 项目负责人： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 联 系 方 式：&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;/h4&gt;&lt;/div&gt;","templateDetailId":"1879804151350157313"}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -822,27 +829,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,23 +867,119 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFD84472"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC80000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC4E59F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B853"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFD84472"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC80000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC4E59F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B853"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1322,24 +1434,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1383,7 +1495,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,18 +1524,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -1438,24 +1550,24 @@
         <v>43</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -1470,24 +1582,24 @@
         <v>43</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>15</v>
@@ -1499,16 +1611,16 @@
         <v>17</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -1516,10 +1628,10 @@
         <v>56</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>15</v>
@@ -1531,7 +1643,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>46</v>
@@ -1540,7 +1652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -1548,10 +1660,10 @@
         <v>57</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -1572,7 +1684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -1580,7 +1692,7 @@
         <v>60</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>15</v>
@@ -1601,18 +1713,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="13" t="s">
         <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>15</v>
@@ -1630,7 +1742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -1638,10 +1750,10 @@
         <v>44</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>15</v>
@@ -1662,7 +1774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="360">
+    <row r="11" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -1670,10 +1782,10 @@
         <v>26</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>15</v>
@@ -1695,7 +1807,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="126">
+    <row r="12" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1703,10 +1815,10 @@
         <v>109</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>15</v>
@@ -1726,7 +1838,7 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="90">
+    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1734,10 +1846,10 @@
         <v>105</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>15</v>
@@ -1760,7 +1872,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="409.6">
+    <row r="14" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1768,10 +1880,10 @@
         <v>29</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>15</v>
@@ -1782,14 +1894,14 @@
       <c r="H14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="13" t="s">
         <v>72</v>
       </c>
       <c r="M14" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="252">
+    <row r="15" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -1797,10 +1909,10 @@
         <v>93</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>15</v>
@@ -1824,7 +1936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="90">
+    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -1832,7 +1944,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>77</v>
@@ -1853,7 +1965,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="90">
+    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -1861,7 +1973,7 @@
         <v>79</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>34</v>
@@ -1882,7 +1994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="90">
+    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -1890,7 +2002,7 @@
         <v>81</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>82</v>
@@ -1911,7 +2023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="90">
+    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -1919,10 +2031,10 @@
         <v>83</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>15</v>
@@ -1940,7 +2052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="90">
+    <row r="20" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -1948,10 +2060,10 @@
         <v>84</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>15</v>
@@ -1969,18 +2081,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="90">
+    <row r="21" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>15</v>
@@ -1998,7 +2110,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="90">
+    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
@@ -2006,10 +2118,10 @@
         <v>86</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>15</v>
@@ -2027,7 +2139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>110</v>
       </c>
@@ -2038,7 +2150,7 @@
         <v>67</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>15</v>
@@ -2056,18 +2168,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>15</v>
@@ -2082,14 +2194,14 @@
       <c r="J24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K24" s="14" t="s">
+      <c r="K24" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="M24" s="15" t="s">
+      <c r="M24" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="409.6">
+    <row r="25" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
@@ -2097,10 +2209,10 @@
         <v>47</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>15</v>
@@ -2111,25 +2223,25 @@
       <c r="H25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="15" t="s">
         <v>198</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="90">
+    <row r="26" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>15</v>
@@ -2153,9 +2265,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>102</v>
@@ -2164,7 +2276,7 @@
         <v>67</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>15</v>
@@ -2185,18 +2297,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="90">
+    <row r="28" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>15</v>
@@ -2215,21 +2327,21 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E28">
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2255,24 +2367,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DF6D78-2EA9-0D4D-A8F7-EC937ACEC0C7}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2316,7 +2428,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
@@ -2345,7 +2457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>128</v>
       </c>
@@ -2356,7 +2468,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -2368,7 +2480,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -2377,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>129</v>
       </c>
@@ -2388,7 +2500,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -2409,7 +2521,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
@@ -2438,7 +2550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>131</v>
       </c>
@@ -2467,7 +2579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>132</v>
       </c>
@@ -2478,7 +2590,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -2499,7 +2611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="360">
+    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>133</v>
       </c>
@@ -2532,7 +2644,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="126">
+    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>134</v>
       </c>
@@ -2563,7 +2675,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="90">
+    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>135</v>
       </c>
@@ -2597,7 +2709,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.6">
+    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>136</v>
       </c>
@@ -2626,7 +2738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="252">
+    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>137</v>
       </c>
@@ -2661,7 +2773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="90">
+    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>138</v>
       </c>
@@ -2690,7 +2802,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="90">
+    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>139</v>
       </c>
@@ -2719,7 +2831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="90">
+    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>140</v>
       </c>
@@ -2748,7 +2860,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="90">
+    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>141</v>
       </c>
@@ -2777,7 +2889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="90">
+    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>142</v>
       </c>
@@ -2806,7 +2918,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="90">
+    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>143</v>
       </c>
@@ -2835,7 +2947,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="90">
+    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>144</v>
       </c>
@@ -2864,7 +2976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>145</v>
       </c>
@@ -2893,7 +3005,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.6">
+    <row r="21" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>146</v>
       </c>
@@ -2922,7 +3034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="90">
+    <row r="22" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>147</v>
       </c>
@@ -2957,7 +3069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>148</v>
       </c>
@@ -2989,7 +3101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -3012,13 +3124,13 @@
         <v>17</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="90">
+    <row r="25" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>150</v>
       </c>
@@ -3053,7 +3165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>151</v>
       </c>
@@ -3085,7 +3197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="90">
+    <row r="27" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>152</v>
       </c>
@@ -3115,21 +3227,21 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3158,25 +3270,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89098C1A-F74A-A24B-BCE4-B3BC9F558B9F}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="11.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="26.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="26.125" style="2" customWidth="1"/>
     <col min="12" max="12" width="35" style="2" customWidth="1"/>
-    <col min="13" max="13" width="45.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="45.625" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="18">
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3220,7 +3332,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -3249,7 +3361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -3260,7 +3372,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -3272,7 +3384,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -3281,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
@@ -3292,7 +3404,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -3313,7 +3425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -3342,7 +3454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -3371,7 +3483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -3382,7 +3494,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -3403,7 +3515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="360">
+    <row r="8" spans="1:14" ht="346.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -3436,7 +3548,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="126">
+    <row r="9" spans="1:14" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>98</v>
       </c>
@@ -3467,7 +3579,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="90">
+    <row r="10" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -3501,7 +3613,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="409.6">
+    <row r="11" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -3523,14 +3635,14 @@
       <c r="H11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>153</v>
+      <c r="J11" s="13" t="s">
+        <v>196</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="252">
+    <row r="12" spans="1:14" ht="247.5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -3565,7 +3677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="90">
+    <row r="13" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -3594,7 +3706,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="90">
+    <row r="14" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -3623,7 +3735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="90">
+    <row r="15" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>33</v>
       </c>
@@ -3652,7 +3764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="90">
+    <row r="16" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -3681,7 +3793,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="90">
+    <row r="17" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>37</v>
       </c>
@@ -3710,7 +3822,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="90">
+    <row r="18" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -3739,7 +3851,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="90">
+    <row r="19" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
@@ -3768,7 +3880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
@@ -3797,134 +3909,184 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="409.6">
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="409.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="90">
-      <c r="A22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1" t="s">
+      <c r="E23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1" t="s">
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L22" s="1"/>
-      <c r="M22" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="L23" s="1"/>
+      <c r="M23" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="E24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="1" t="s">
+      <c r="H24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="1">
+      <c r="M24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="90">
-      <c r="A24" s="1" t="s">
+    <row r="25" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1" t="s">
+      <c r="E25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="1" t="s">
+      <c r="H25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M25" s="5" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E24">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="E2:E20 E22:E25">
+    <cfRule type="cellIs" dxfId="14" priority="11" operator="equal">
+      <formula>"P5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
+      <formula>"P4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+      <formula>"P3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+      <formula>"P2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="15" operator="equal">
+      <formula>"P1"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
@@ -3942,22 +4104,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E24" xr:uid="{CA2D7B4E-0B5D-9B42-80A9-A35F2786EBB3}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E25" xr:uid="{CA2D7B4E-0B5D-9B42-80A9-A35F2786EBB3}">
       <formula1>"P1,P2,P3,P4,P5"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVO1:WVO7 WLS1:WLS7 WBW1:WBW7 VSA1:VSA7 VIE1:VIE7 UYI1:UYI7 UOM1:UOM7 UEQ1:UEQ7 TUU1:TUU7 TKY1:TKY7 TBC1:TBC7 SRG1:SRG7 SHK1:SHK7 RXO1:RXO7 RNS1:RNS7 RDW1:RDW7 QUA1:QUA7 QKE1:QKE7 QAI1:QAI7 PQM1:PQM7 PGQ1:PGQ7 OWU1:OWU7 OMY1:OMY7 ODC1:ODC7 NTG1:NTG7 NJK1:NJK7 MZO1:MZO7 MPS1:MPS7 MFW1:MFW7 LWA1:LWA7 LME1:LME7 LCI1:LCI7 KSM1:KSM7 KIQ1:KIQ7 JYU1:JYU7 JOY1:JOY7 JFC1:JFC7 IVG1:IVG7 ILK1:ILK7 IBO1:IBO7 HRS1:HRS7 HHW1:HHW7 GYA1:GYA7 GOE1:GOE7 GEI1:GEI7 FUM1:FUM7 FKQ1:FKQ7 FAU1:FAU7 EQY1:EQY7 EHC1:EHC7 DXG1:DXG7 DNK1:DNK7 DDO1:DDO7 CTS1:CTS7 CJW1:CJW7 CAA1:CAA7 BQE1:BQE7 BGI1:BGI7 AWM1:AWM7 AMQ1:AMQ7 ACU1:ACU7 SY1:SY7 JC1:JC7 WVO20 WLS20 WBW20 VSA20 VIE20 UYI20 UOM20 UEQ20 TUU20 TKY20 TBC20 SRG20 SHK20 RXO20 RNS20 RDW20 QUA20 QKE20 QAI20 PQM20 PGQ20 OWU20 OMY20 ODC20 NTG20 NJK20 MZO20 MPS20 MFW20 LWA20 LME20 LCI20 KSM20 KIQ20 JYU20 JOY20 JFC20 IVG20 ILK20 IBO20 HRS20 HHW20 GYA20 GOE20 GEI20 FUM20 FKQ20 FAU20 EQY20 EHC20 DXG20 DNK20 DDO20 CTS20 CJW20 CAA20 BQE20 BGI20 AWM20 AMQ20 ACU20 SY20 JC20 WVO23 WLS23 WBW23 VSA23 VIE23 UYI23 UOM23 UEQ23 TUU23 TKY23 TBC23 SRG23 SHK23 RXO23 RNS23 RDW23 QUA23 QKE23 QAI23 PQM23 PGQ23 OWU23 OMY23 ODC23 NTG23 NJK23 MZO23 MPS23 MFW23 LWA23 LME23 LCI23 KSM23 KIQ23 JYU23 JOY23 JFC23 IVG23 ILK23 IBO23 HRS23 HHW23 GYA23 GOE23 GEI23 FUM23 FKQ23 FAU23 EQY23 EHC23 DXG23 DNK23 DDO23 CTS23 CJW23 CAA23 BQE23 BGI23 AWM23 AMQ23 ACU23 SY23 JC23 H1:H24" xr:uid="{DEE60292-F00A-574F-AB8D-6191ACA0BB1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVO1:WVO7 WLS1:WLS7 WBW1:WBW7 VSA1:VSA7 VIE1:VIE7 UYI1:UYI7 UOM1:UOM7 UEQ1:UEQ7 TUU1:TUU7 TKY1:TKY7 TBC1:TBC7 SRG1:SRG7 SHK1:SHK7 RXO1:RXO7 RNS1:RNS7 RDW1:RDW7 QUA1:QUA7 QKE1:QKE7 QAI1:QAI7 PQM1:PQM7 PGQ1:PGQ7 OWU1:OWU7 OMY1:OMY7 ODC1:ODC7 NTG1:NTG7 NJK1:NJK7 MZO1:MZO7 MPS1:MPS7 MFW1:MFW7 LWA1:LWA7 LME1:LME7 LCI1:LCI7 KSM1:KSM7 KIQ1:KIQ7 JYU1:JYU7 JOY1:JOY7 JFC1:JFC7 IVG1:IVG7 ILK1:ILK7 IBO1:IBO7 HRS1:HRS7 HHW1:HHW7 GYA1:GYA7 GOE1:GOE7 GEI1:GEI7 FUM1:FUM7 FKQ1:FKQ7 FAU1:FAU7 EQY1:EQY7 EHC1:EHC7 DXG1:DXG7 DNK1:DNK7 DDO1:DDO7 CTS1:CTS7 CJW1:CJW7 CAA1:CAA7 BQE1:BQE7 BGI1:BGI7 AWM1:AWM7 AMQ1:AMQ7 ACU1:ACU7 SY1:SY7 JC1:JC7 WBW20:WBW21 VSA20:VSA21 VIE20:VIE21 UYI20:UYI21 UOM20:UOM21 UEQ20:UEQ21 TUU20:TUU21 TKY20:TKY21 TBC20:TBC21 SRG20:SRG21 SHK20:SHK21 RXO20:RXO21 RNS20:RNS21 RDW20:RDW21 QUA20:QUA21 QKE20:QKE21 QAI20:QAI21 PQM20:PQM21 PGQ20:PGQ21 OWU20:OWU21 OMY20:OMY21 ODC20:ODC21 NTG20:NTG21 NJK20:NJK21 MZO20:MZO21 MPS20:MPS21 MFW20:MFW21 LWA20:LWA21 LME20:LME21 LCI20:LCI21 KSM20:KSM21 KIQ20:KIQ21 JYU20:JYU21 JOY20:JOY21 JFC20:JFC21 IVG20:IVG21 ILK20:ILK21 IBO20:IBO21 HRS20:HRS21 HHW20:HHW21 GYA20:GYA21 GOE20:GOE21 GEI20:GEI21 FUM20:FUM21 FKQ20:FKQ21 FAU20:FAU21 EQY20:EQY21 EHC20:EHC21 DXG20:DXG21 DNK20:DNK21 DDO20:DDO21 CTS20:CTS21 CJW20:CJW21 CAA20:CAA21 BQE20:BQE21 BGI20:BGI21 AWM20:AWM21 AMQ20:AMQ21 ACU20:ACU21 SY20:SY21 JC20:JC21 WVO24 WLS24 WBW24 VSA24 VIE24 UYI24 UOM24 UEQ24 TUU24 TKY24 TBC24 SRG24 SHK24 RXO24 RNS24 RDW24 QUA24 QKE24 QAI24 PQM24 PGQ24 OWU24 OMY24 ODC24 NTG24 NJK24 MZO24 MPS24 MFW24 LWA24 LME24 LCI24 KSM24 KIQ24 JYU24 JOY24 JFC24 IVG24 ILK24 IBO24 HRS24 HHW24 GYA24 GOE24 GEI24 FUM24 FKQ24 FAU24 EQY24 EHC24 DXG24 DNK24 DDO24 CTS24 CJW24 CAA24 BQE24 BGI24 AWM24 AMQ24 ACU24 SY24 JC24 WVO20:WVO21 H1:H25 WLS20:WLS21" xr:uid="{DEE60292-F00A-574F-AB8D-6191ACA0BB1D}">
       <formula1>"params,data,json"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVN1:WVN7 WLR1:WLR7 WBV1:WBV7 VRZ1:VRZ7 VID1:VID7 UYH1:UYH7 UOL1:UOL7 UEP1:UEP7 TUT1:TUT7 TKX1:TKX7 TBB1:TBB7 SRF1:SRF7 SHJ1:SHJ7 RXN1:RXN7 RNR1:RNR7 RDV1:RDV7 QTZ1:QTZ7 QKD1:QKD7 QAH1:QAH7 PQL1:PQL7 PGP1:PGP7 OWT1:OWT7 OMX1:OMX7 ODB1:ODB7 NTF1:NTF7 NJJ1:NJJ7 MZN1:MZN7 MPR1:MPR7 MFV1:MFV7 LVZ1:LVZ7 LMD1:LMD7 LCH1:LCH7 KSL1:KSL7 KIP1:KIP7 JYT1:JYT7 JOX1:JOX7 JFB1:JFB7 IVF1:IVF7 ILJ1:ILJ7 IBN1:IBN7 HRR1:HRR7 HHV1:HHV7 GXZ1:GXZ7 GOD1:GOD7 GEH1:GEH7 FUL1:FUL7 FKP1:FKP7 FAT1:FAT7 EQX1:EQX7 EHB1:EHB7 DXF1:DXF7 DNJ1:DNJ7 DDN1:DDN7 CTR1:CTR7 CJV1:CJV7 BZZ1:BZZ7 BQD1:BQD7 BGH1:BGH7 AWL1:AWL7 AMP1:AMP7 ACT1:ACT7 SX1:SX7 JB1:JB7 WVN20 WLR20 WBV20 VRZ20 VID20 UYH20 UOL20 UEP20 TUT20 TKX20 TBB20 SRF20 SHJ20 RXN20 RNR20 RDV20 QTZ20 QKD20 QAH20 PQL20 PGP20 OWT20 OMX20 ODB20 NTF20 NJJ20 MZN20 MPR20 MFV20 LVZ20 LMD20 LCH20 KSL20 KIP20 JYT20 JOX20 JFB20 IVF20 ILJ20 IBN20 HRR20 HHV20 GXZ20 GOD20 GEH20 FUL20 FKP20 FAT20 EQX20 EHB20 DXF20 DNJ20 DDN20 CTR20 CJV20 BZZ20 BQD20 BGH20 AWL20 AMP20 ACT20 SX20 JB20 WVN23 WLR23 WBV23 VRZ23 VID23 UYH23 UOL23 UEP23 TUT23 TKX23 TBB23 SRF23 SHJ23 RXN23 RNR23 RDV23 QTZ23 QKD23 QAH23 PQL23 PGP23 OWT23 OMX23 ODB23 NTF23 NJJ23 MZN23 MPR23 MFV23 LVZ23 LMD23 LCH23 KSL23 KIP23 JYT23 JOX23 JFB23 IVF23 ILJ23 IBN23 HRR23 HHV23 GXZ23 GOD23 GEH23 FUL23 FKP23 FAT23 EQX23 EHB23 DXF23 DNJ23 DDN23 CTR23 CJV23 BZZ23 BQD23 BGH23 AWL23 AMP23 ACT23 SX23 JB23 G1:G24" xr:uid="{F397FF35-DC5F-6B46-ACA6-59606BB30C9B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVN1:WVN7 WLR1:WLR7 WBV1:WBV7 VRZ1:VRZ7 VID1:VID7 UYH1:UYH7 UOL1:UOL7 UEP1:UEP7 TUT1:TUT7 TKX1:TKX7 TBB1:TBB7 SRF1:SRF7 SHJ1:SHJ7 RXN1:RXN7 RNR1:RNR7 RDV1:RDV7 QTZ1:QTZ7 QKD1:QKD7 QAH1:QAH7 PQL1:PQL7 PGP1:PGP7 OWT1:OWT7 OMX1:OMX7 ODB1:ODB7 NTF1:NTF7 NJJ1:NJJ7 MZN1:MZN7 MPR1:MPR7 MFV1:MFV7 LVZ1:LVZ7 LMD1:LMD7 LCH1:LCH7 KSL1:KSL7 KIP1:KIP7 JYT1:JYT7 JOX1:JOX7 JFB1:JFB7 IVF1:IVF7 ILJ1:ILJ7 IBN1:IBN7 HRR1:HRR7 HHV1:HHV7 GXZ1:GXZ7 GOD1:GOD7 GEH1:GEH7 FUL1:FUL7 FKP1:FKP7 FAT1:FAT7 EQX1:EQX7 EHB1:EHB7 DXF1:DXF7 DNJ1:DNJ7 DDN1:DDN7 CTR1:CTR7 CJV1:CJV7 BZZ1:BZZ7 BQD1:BQD7 BGH1:BGH7 AWL1:AWL7 AMP1:AMP7 ACT1:ACT7 SX1:SX7 JB1:JB7 WBV20:WBV21 VRZ20:VRZ21 VID20:VID21 UYH20:UYH21 UOL20:UOL21 UEP20:UEP21 TUT20:TUT21 TKX20:TKX21 TBB20:TBB21 SRF20:SRF21 SHJ20:SHJ21 RXN20:RXN21 RNR20:RNR21 RDV20:RDV21 QTZ20:QTZ21 QKD20:QKD21 QAH20:QAH21 PQL20:PQL21 PGP20:PGP21 OWT20:OWT21 OMX20:OMX21 ODB20:ODB21 NTF20:NTF21 NJJ20:NJJ21 MZN20:MZN21 MPR20:MPR21 MFV20:MFV21 LVZ20:LVZ21 LMD20:LMD21 LCH20:LCH21 KSL20:KSL21 KIP20:KIP21 JYT20:JYT21 JOX20:JOX21 JFB20:JFB21 IVF20:IVF21 ILJ20:ILJ21 IBN20:IBN21 HRR20:HRR21 HHV20:HHV21 GXZ20:GXZ21 GOD20:GOD21 GEH20:GEH21 FUL20:FUL21 FKP20:FKP21 FAT20:FAT21 EQX20:EQX21 EHB20:EHB21 DXF20:DXF21 DNJ20:DNJ21 DDN20:DDN21 CTR20:CTR21 CJV20:CJV21 BZZ20:BZZ21 BQD20:BQD21 BGH20:BGH21 AWL20:AWL21 AMP20:AMP21 ACT20:ACT21 SX20:SX21 JB20:JB21 WVN24 WLR24 WBV24 VRZ24 VID24 UYH24 UOL24 UEP24 TUT24 TKX24 TBB24 SRF24 SHJ24 RXN24 RNR24 RDV24 QTZ24 QKD24 QAH24 PQL24 PGP24 OWT24 OMX24 ODB24 NTF24 NJJ24 MZN24 MPR24 MFV24 LVZ24 LMD24 LCH24 KSL24 KIP24 JYT24 JOX24 JFB24 IVF24 ILJ24 IBN24 HRR24 HHV24 GXZ24 GOD24 GEH24 FUL24 FKP24 FAT24 EQX24 EHB24 DXF24 DNJ24 DDN24 CTR24 CJV24 BZZ24 BQD24 BGH24 AWL24 AMP24 ACT24 SX24 JB24 WVN20:WVN21 G1:G25 WLR20:WLR21" xr:uid="{F397FF35-DC5F-6B46-ACA6-59606BB30C9B}">
       <formula1>"get,post,put,delete,head,options,patch"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA1:JA7 WVM1:WVM7 WLQ1:WLQ7 WBU1:WBU7 VRY1:VRY7 VIC1:VIC7 UYG1:UYG7 UOK1:UOK7 UEO1:UEO7 TUS1:TUS7 TKW1:TKW7 TBA1:TBA7 SRE1:SRE7 SHI1:SHI7 RXM1:RXM7 RNQ1:RNQ7 RDU1:RDU7 QTY1:QTY7 QKC1:QKC7 QAG1:QAG7 PQK1:PQK7 PGO1:PGO7 OWS1:OWS7 OMW1:OMW7 ODA1:ODA7 NTE1:NTE7 NJI1:NJI7 MZM1:MZM7 MPQ1:MPQ7 MFU1:MFU7 LVY1:LVY7 LMC1:LMC7 LCG1:LCG7 KSK1:KSK7 KIO1:KIO7 JYS1:JYS7 JOW1:JOW7 JFA1:JFA7 IVE1:IVE7 ILI1:ILI7 IBM1:IBM7 HRQ1:HRQ7 HHU1:HHU7 GXY1:GXY7 GOC1:GOC7 GEG1:GEG7 FUK1:FUK7 FKO1:FKO7 FAS1:FAS7 EQW1:EQW7 EHA1:EHA7 DXE1:DXE7 DNI1:DNI7 DDM1:DDM7 CTQ1:CTQ7 CJU1:CJU7 BZY1:BZY7 BQC1:BQC7 BGG1:BGG7 AWK1:AWK7 AMO1:AMO7 ACS1:ACS7 SW1:SW7 WVM20 WLQ20 WBU20 VRY20 VIC20 UYG20 UOK20 UEO20 TUS20 TKW20 TBA20 SRE20 SHI20 RXM20 RNQ20 RDU20 QTY20 QKC20 QAG20 PQK20 PGO20 OWS20 OMW20 ODA20 NTE20 NJI20 MZM20 MPQ20 MFU20 LVY20 LMC20 LCG20 KSK20 KIO20 JYS20 JOW20 JFA20 IVE20 ILI20 IBM20 HRQ20 HHU20 GXY20 GOC20 GEG20 FUK20 FKO20 FAS20 EQW20 EHA20 DXE20 DNI20 DDM20 CTQ20 CJU20 BZY20 BQC20 BGG20 AWK20 AMO20 ACS20 SW20 JA20 WVM23 WLQ23 WBU23 VRY23 VIC23 UYG23 UOK23 UEO23 TUS23 TKW23 TBA23 SRE23 SHI23 RXM23 RNQ23 RDU23 QTY23 QKC23 QAG23 PQK23 PGO23 OWS23 OMW23 ODA23 NTE23 NJI23 MZM23 MPQ23 MFU23 LVY23 LMC23 LCG23 KSK23 KIO23 JYS23 JOW23 JFA23 IVE23 ILI23 IBM23 HRQ23 HHU23 GXY23 GOC23 GEG23 FUK23 FKO23 FAS23 EQW23 EHA23 DXE23 DNI23 DDM23 CTQ23 CJU23 BZY23 BQC23 BGG23 AWK23 AMO23 ACS23 SW23 JA23" xr:uid="{1DEF28CA-FCD9-3448-8096-0EA5A5D69C3F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="JA1:JA7 WVM1:WVM7 WLQ1:WLQ7 WBU1:WBU7 VRY1:VRY7 VIC1:VIC7 UYG1:UYG7 UOK1:UOK7 UEO1:UEO7 TUS1:TUS7 TKW1:TKW7 TBA1:TBA7 SRE1:SRE7 SHI1:SHI7 RXM1:RXM7 RNQ1:RNQ7 RDU1:RDU7 QTY1:QTY7 QKC1:QKC7 QAG1:QAG7 PQK1:PQK7 PGO1:PGO7 OWS1:OWS7 OMW1:OMW7 ODA1:ODA7 NTE1:NTE7 NJI1:NJI7 MZM1:MZM7 MPQ1:MPQ7 MFU1:MFU7 LVY1:LVY7 LMC1:LMC7 LCG1:LCG7 KSK1:KSK7 KIO1:KIO7 JYS1:JYS7 JOW1:JOW7 JFA1:JFA7 IVE1:IVE7 ILI1:ILI7 IBM1:IBM7 HRQ1:HRQ7 HHU1:HHU7 GXY1:GXY7 GOC1:GOC7 GEG1:GEG7 FUK1:FUK7 FKO1:FKO7 FAS1:FAS7 EQW1:EQW7 EHA1:EHA7 DXE1:DXE7 DNI1:DNI7 DDM1:DDM7 CTQ1:CTQ7 CJU1:CJU7 BZY1:BZY7 BQC1:BQC7 BGG1:BGG7 AWK1:AWK7 AMO1:AMO7 ACS1:ACS7 SW1:SW7 WBU20:WBU21 VRY20:VRY21 VIC20:VIC21 UYG20:UYG21 UOK20:UOK21 UEO20:UEO21 TUS20:TUS21 TKW20:TKW21 TBA20:TBA21 SRE20:SRE21 SHI20:SHI21 RXM20:RXM21 RNQ20:RNQ21 RDU20:RDU21 QTY20:QTY21 QKC20:QKC21 QAG20:QAG21 PQK20:PQK21 PGO20:PGO21 OWS20:OWS21 OMW20:OMW21 ODA20:ODA21 NTE20:NTE21 NJI20:NJI21 MZM20:MZM21 MPQ20:MPQ21 MFU20:MFU21 LVY20:LVY21 LMC20:LMC21 LCG20:LCG21 KSK20:KSK21 KIO20:KIO21 JYS20:JYS21 JOW20:JOW21 JFA20:JFA21 IVE20:IVE21 ILI20:ILI21 IBM20:IBM21 HRQ20:HRQ21 HHU20:HHU21 GXY20:GXY21 GOC20:GOC21 GEG20:GEG21 FUK20:FUK21 FKO20:FKO21 FAS20:FAS21 EQW20:EQW21 EHA20:EHA21 DXE20:DXE21 DNI20:DNI21 DDM20:DDM21 CTQ20:CTQ21 CJU20:CJU21 BZY20:BZY21 BQC20:BQC21 BGG20:BGG21 AWK20:AWK21 AMO20:AMO21 ACS20:ACS21 SW20:SW21 JA20:JA21 WVM20:WVM21 JA24 WVM24 WLQ24 WBU24 VRY24 VIC24 UYG24 UOK24 UEO24 TUS24 TKW24 TBA24 SRE24 SHI24 RXM24 RNQ24 RDU24 QTY24 QKC24 QAG24 PQK24 PGO24 OWS24 OMW24 ODA24 NTE24 NJI24 MZM24 MPQ24 MFU24 LVY24 LMC24 LCG24 KSK24 KIO24 JYS24 JOW24 JFA24 IVE24 ILI24 IBM24 HRQ24 HHU24 GXY24 GOC24 GEG24 FUK24 FKO24 FAS24 EQW24 EHA24 DXE24 DNI24 DDM24 CTQ24 CJU24 BZY24 BQC24 BGG24 AWK24 AMO24 ACS24 SW24 WLQ20:WLQ21" xr:uid="{1DEF28CA-FCD9-3448-8096-0EA5A5D69C3F}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D17" r:id="rId1" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfId}" xr:uid="{7A9AD3BC-7E48-9C4C-9F29-35DC615A8BBA}"/>
-    <hyperlink ref="D21" r:id="rId2" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfid}" xr:uid="{7832EB21-AA14-9946-908E-FC3BE5403316}"/>
+    <hyperlink ref="D22" r:id="rId2" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfid}" xr:uid="{7832EB21-AA14-9946-908E-FC3BE5403316}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
